--- a/daily_matches/job_matches_2026-05-14.xlsx
+++ b/daily_matches/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GenAI and Agentic AI Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Hyperlight</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Cortex, TensorFlow, PyTorch, Keras, Azure ML</t>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, S3, EC2, Glue, Data Lake, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f130ec0d2686bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d8a2e8f953d307</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Text and Speech Analyst</t>
+          <t>Senior Engineer - Applied AI (Java)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,204 +521,204 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Cortex, TensorFlow, PyTorch, Keras, Azure ML, Git, Snowflake, Databricks, Power BI</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6519802f75a6e831</t>
+          <t>https://www.indeed.com/viewjob?jk=e44e70b564ebc32c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Engineer - Applied AI (Java)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca67cc261c055a24</t>
+          <t>https://www.indeed.com/viewjob?jk=bb30a8f4ea693783</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EverCommerce - Senior Data Engineer</t>
+          <t>Senior Engineer - Applied AI (Java)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Athena, Data Lake, Apache Airflow, Git, Databricks, Kafka, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
+          <t>https://www.indeed.com/viewjob?jk=cb185f247947f1b1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer-Infrastructure</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Git, BigQuery, Kafka, Hadoop, Matplotlib, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Architect &amp; Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Electrosoft Services Inc</t>
+          <t>Alera Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Redshift, Synapse, Databricks, Redshift, Tableau, Power BI, Python</t>
+          <t>RAG, Copilot, Pinecone, S3, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d06c8026905991f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b92726ea7c893d3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ML Ops Engineer (Boston, MA)</t>
+          <t>Senior AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>Generative AI, RAG, S3, Kubernetes, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5e03d45c925bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Site Reliability Engineer - AI &amp; ML Infrastructure (Kubernetes, AWS &amp; Terraform)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The New IEM, LLC</t>
+          <t>Deepgram</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
+          <t>https://www.indeed.com/viewjob?jk=9afb2863f44a03b2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Governance &amp; Explainability Engineer</t>
+          <t>Senior Software Engineer - AI Native Platform</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Cortex, Azure ML, CI/CD, Git, Snowflake, Databricks, Power BI, Python</t>
+          <t>LangChain, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f3527ce1aafed4</t>
+          <t>https://www.indeed.com/viewjob?jk=78997836495aa690</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java/Angular Developer - AI Enabled Platform (Contract) REMOTE</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, Jenkins, Git, Snowflake, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9360706927667c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9388af12e6c1cbb9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Global Payment Network)</t>
+          <t>Sr. Security Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Kubernetes, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42cb2235e928c1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c3b4f437b4e397</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Analyst, Global Scaled Growth</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+          <t>CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,42 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7d5cf500a5a35b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Science Senior Associate - Card Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aef8c9ea7df32c71</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-14.xlsx
+++ b/daily_matches/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior AI/ML Architect, Applied Field Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hyperlight</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, S3, EC2, Glue, Data Lake, Docker</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d8a2e8f953d307</t>
+          <t>https://www.indeed.com/viewjob?jk=0ee38a91bb7a00d3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer - Applied AI (Java)</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Kubernetes, CI/CD, Terraform, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,392 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e44e70b564ebc32c</t>
+          <t>https://www.indeed.com/viewjob?jk=d01d7a6b9f146106</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer - Applied AI (Java)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, CI/CD, Git, Databricks, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb30a8f4ea693783</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Applied AI (Java)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb185f247947f1b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Software Engineer-Infrastructure</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB, Python</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior AI Architect &amp; Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Alera Group</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Pinecone, S3, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b92726ea7c893d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior AWS Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>State Farm</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bloomington, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, S3, Kubernetes, Terraform, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer - AI &amp; ML Infrastructure (Kubernetes, AWS &amp; Terraform)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Deepgram</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, S3, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9afb2863f44a03b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - AI Native Platform</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CloudBees Inc</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78997836495aa690</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Mutual of Omaha</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, CI/CD, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9388af12e6c1cbb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sr. Security Data Scientist</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Illumio</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Kubernetes, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c3b4f437b4e397</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>EchoStar</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Science Senior Associate - Card Data &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aef8c9ea7df32c71</t>
+          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-14.xlsx
+++ b/daily_matches/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI/ML Architect, Applied Field Engineering</t>
+          <t>Agentic AI Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Snowflake, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, FAISS, Pinecone, Prompt Engineering, S3, Glue, Athena, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ee38a91bb7a00d3</t>
+          <t>https://www.indeed.com/viewjob?jk=cf62a60610273c1a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Software Engineer IV - AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SEACORP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Middletown, RI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Kubernetes, CI/CD, Terraform, Git, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone, ChromaDB, PyTorch, MLflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,742 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01d7a6b9f146106</t>
+          <t>https://www.indeed.com/viewjob?jk=49f31298f7c4c39d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8ce81ab377f28cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Progyny</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>S3, EC2, FastAPI, Docker, CI/CD, Terraform, Git, Snowflake, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Associate Test Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a4fe70a1dad5e45</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JSR Tech Consulting</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, Kinesis, Jenkins, Git, Redshift, MySQL, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b60af712b26a5dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>David's Bridal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, EC2, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=096d88ecac141a5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Riverain Technologies</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer - Global CI/CD Platform</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Transamerica</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cedar Rapids, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer / SDET( Only local to NY/NJ/CT)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sunsoft Services Inc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1ceed29293bf031</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Linux Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdd9a77f8957015f</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b651b9a2820a9eb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Research Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Oak Ridge National Laboratory</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Oak Ridge, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, S3, MLflow, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d4568c7426270e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PLTR Developer- Remote</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cystems Logic Inc</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sr AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f54f4547c27b9425</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10a4c8d06317d6d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=947359a0b3fdceac</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sr AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1fa47c4c42761ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Solution Architect</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, FastAPI, CI/CD, Git, Snowflake, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce0b808628596f38</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Redshift, AKS, Terraform, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb3cf832b1fc4af0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data &amp; AI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kinetic Plc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Data Lake, Apache Airflow, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12ba0ee69b417970</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pacers Sports &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28f603a4feed3077</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-14.xlsx
+++ b/daily_matches/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Agentic AI Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, FAISS, Pinecone, Prompt Engineering, S3, Glue, Athena, Redshift</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, S3, Athena, Redshift, Kinesis, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf62a60610273c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e58ec0c3fb594e76</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer IV - AI</t>
+          <t>DATA SCIENTIST L3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SEACORP</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Middletown, RI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone, ChromaDB, PyTorch, MLflow</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f31298f7c4c39d</t>
+          <t>https://www.indeed.com/viewjob?jk=086bdc410d438299</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
+          <t>RAG, Redshift, Git, Snowflake, Redshift, Kafka, Hadoop, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ce81ab377f28cb</t>
+          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer, AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Progyny</t>
+          <t>Leadfeeder</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, EC2, FastAPI, Docker, CI/CD, Terraform, Git, Snowflake, PostgreSQL, MySQL</t>
+          <t>S3, Glue, Athena, Redshift, BigQuery, Apache Airflow, CI/CD, Snowflake, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Test Automation Engineer</t>
+          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4fe70a1dad5e45</t>
+          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Redshift, Kinesis, Jenkins, Git, Redshift, MySQL, NoSQL, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b60af712b26a5dd</t>
+          <t>https://www.indeed.com/viewjob?jk=941f6f7fd943a71b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior DataOps Engineer- Remote US</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, EC2, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096d88ecac141a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Riverain Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>Copilot, Docker, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
+          <t>https://www.indeed.com/viewjob?jk=3dd34108238bba72</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Global CI/CD Platform</t>
+          <t>Senior Platforms Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, MongoDB, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
+          <t>https://www.indeed.com/viewjob?jk=30097aa5f8e654fe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QA Automation Engineer / SDET( Only local to NY/NJ/CT)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sunsoft Services Inc</t>
+          <t>Conga</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R</t>
+          <t>LangChain, RAG, TensorFlow, PyTorch, FastAPI, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1ceed29293bf031</t>
+          <t>https://www.indeed.com/viewjob?jk=c228653fa007afb0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Linux Systems Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Conga</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
+          <t>LangChain, RAG, TensorFlow, PyTorch, FastAPI, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd9a77f8957015f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ffd9c6aa0b38724</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tucows</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b651b9a2820a9eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=a435e932c79779ff</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Research Software Engineer</t>
+          <t>Data Scientist - GenBI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oak Ridge National Laboratory</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
+          <t>Data Scientist, RAG, BigQuery, Databricks, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4568c7426270e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e56049102b2b42b9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PLTR Developer- Remote</t>
+          <t>Senior Platform Backend Engineer - Battery Storage</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>Plus Power</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>The Woodlands, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
+          <t>https://www.indeed.com/viewjob?jk=fe161d0adfb46d1e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr AI Machine Learning Engineer</t>
+          <t>Senior Front-End Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Mochi Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, Git, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f54f4547c27b9425</t>
+          <t>https://www.indeed.com/viewjob?jk=b8da7f72cb314f40</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr AI Machine Learning Engineer</t>
+          <t>Sr. Backend Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Mochi Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a4c8d06317d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=1590f822d96f2b45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr AI Machine Learning Engineer</t>
+          <t>Data &amp; AI Solution Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947359a0b3fdceac</t>
+          <t>https://www.indeed.com/viewjob?jk=194d364c0d8dad1f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr AI Machine Learning Engineer</t>
+          <t>Data &amp; AI Solution Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa47c4c42761ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7b9b2d221eceab1f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Data &amp; AI Solution Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, FastAPI, CI/CD, Git, Snowflake, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce0b808628596f38</t>
+          <t>https://www.indeed.com/viewjob?jk=eaafd47b353a91f7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; AI Solution Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, AKS, Terraform, Redshift, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb3cf832b1fc4af0</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8ce98c64e32277</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, Data &amp; AI</t>
+          <t>Data &amp; AI Solution Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kinetic Plc</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Weymouth, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, Apache Airflow, CI/CD, Terraform, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ba0ee69b417970</t>
+          <t>https://www.indeed.com/viewjob?jk=33d305ed12d954bc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data &amp; AI Solution Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
+          <t>https://www.indeed.com/viewjob?jk=cd46699a4e4213ff</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Data &amp; AI Solution Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,682 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f603a4feed3077</t>
+          <t>https://www.indeed.com/viewjob?jk=7b889a2aa7f5795a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hillsboro, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a0daff83b9d4f74</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28b554e93b37c200</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cce5bed00f159463</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3930788cfbbb793f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Collegeville, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09db2bc18c0e0f6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f77c19143557e03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe515b441eecf4eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sellersburg, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12291fa7adfa5767</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46007368e6a5ba17</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=352c77b07f81294b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Barnegat, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=337cbf9bd58b16cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wildwood, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4597e53ab4ea8a5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=152431b86dc2d2f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aca07882f9b54637</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chaska, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5b61510b900be91</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=444cff7fbc716680</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Fennville, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38394355da4e6a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Integrity Marketing Group</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Urbandale, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65ac40d325ea3c56</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer, Workflow Systems</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>hatch IT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d2e7d2be831d3d7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-14.xlsx
+++ b/daily_matches/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>GenAI &amp; Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, AWS SageMaker, S3, Glue, Docker, Kubernetes</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e9af94a5ec5657</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Industrial Data Engineer</t>
+          <t>AI Application Development Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Esi solutions</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sisters, OR, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Databricks, PostgreSQL, MySQL, Tableau, Power BI, Python</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4677bac9c152c55d</t>
+          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer - Mid/Sr.</t>
+          <t>Referral Only -Reports Developer (Spotfire)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Redshift, CI/CD, Git, Redshift, Quicksight, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae5bcd4793ab2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb0b8fa50ac2102</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>SRE Infrastructure Engineer | SFO, CA (5 Days Onsite) | contract W2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ecebd01962f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8c23dedffefb4b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Cognitive Analytics Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
+          <t>AI Engineer, RAG, PyTorch, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea58734723211dbf</t>
+          <t>https://www.indeed.com/viewjob?jk=c551bda472d34db1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, S3, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abab67b71064e59</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba1ba40eb5f4659</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solution Architect - Agentic AI &amp; Data</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, S3, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ff4c0a4ad2707f</t>
+          <t>https://www.indeed.com/viewjob?jk=53d5e7828dfdbdfc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Slater Infrastructure Group</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ridgeland, MS, US USA</t>
+          <t>Ellendale, ND, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Gemini, CI/CD, Terraform, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b6b4a936e8108f</t>
+          <t>https://www.indeed.com/viewjob?jk=7339a7b55f8b50e4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Averna</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Harwood, ND, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, BigQuery, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09c247b71f8052bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2b24ee619b99910f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer _ GitHub Copilot Agents (Salesforce Development &amp; Testing)</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Ellendale, ND, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Optimization</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f81cc7b7dfa96c66</t>
+          <t>https://www.indeed.com/viewjob?jk=24fd4c742bcbc08b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azure Software Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Altigen Technologies</t>
+          <t>Applied Digital</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c33a5181d22295ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c801f0bbf0744f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Early Careers Rotational Program - R&amp;D Engineer (AI)</t>
+          <t>AI Accelerator - Programmer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VIAVI Solutions</t>
+          <t>University of California - San Francisco</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Docker, Kubernetes, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, CI/CD, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af0593309820315</t>
+          <t>https://www.indeed.com/viewjob?jk=f7020434941a1065</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Developer - US Based Remote Opportunity</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Common App</t>
+          <t>ABCO COMPUTERS PVT LTD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Jenkins, Git, Python, SQL, R, Optimization</t>
+          <t>Copilot, S3, EC2, Redshift, CI/CD, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b945a88bd9dbab2</t>
+          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fraud / Credit Data Scientist, Risk Solutions</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LightGBM, AWS SageMaker, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, BigQuery, Dataflow, Kubernetes, Git, BigQuery, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,112 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f3f0c9a5dfc77b</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac9657901f0cf43</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Clearwater Analytics (CWAN)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Kafka, Cassandra, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc44cf9da3246f4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Test Automation Engineer - Python/Pytest</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, CI/CD, Jenkins, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f093cd57d294f5d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Spectrio LLC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d71938ac4bcc1c1</t>
         </is>
       </c>
     </row>
